--- a/ig/DM-JUIN-2026/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM-JUIN-2026/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T07:49:26+00:00</t>
+    <t>2026-06-12T13:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUIN-2026/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM-JUIN-2026/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T13:45:34+00:00</t>
+    <t>2026-06-12T15:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUIN-2026/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM-JUIN-2026/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:52:07+00:00</t>
+    <t>2026-06-16T11:18:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUIN-2026/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM-JUIN-2026/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T11:18:28+00:00</t>
+    <t>2026-06-18T08:54:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUIN-2026/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM-JUIN-2026/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:54:40+00:00</t>
+    <t>2026-06-19T10:20:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUIN-2026/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM-JUIN-2026/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T10:20:09+00:00</t>
+    <t>2026-06-19T14:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUIN-2026/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM-JUIN-2026/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:33:59+00:00</t>
+    <t>2026-06-22T07:17:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUIN-2026/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM-JUIN-2026/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T07:17:41+00:00</t>
+    <t>2026-06-22T15:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUIN-2026/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM-JUIN-2026/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T15:36:30+00:00</t>
+    <t>2026-06-23T15:08:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUIN-2026/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM-JUIN-2026/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T15:08:52+00:00</t>
+    <t>2026-06-24T09:29:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUIN-2026/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM-JUIN-2026/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T09:29:27+00:00</t>
+    <t>2026-06-25T16:03:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUIN-2026/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM-JUIN-2026/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T16:03:31+00:00</t>
+    <t>2026-06-26T08:50:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
